--- a/data/trans_dic/P62A$jubilacion-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P62A$jubilacion-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de jubilación</t>
+          <t>Población que, al menos, percibe una pensión de jubilación (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,64; 92,81</t>
+          <t>87,54; 92,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,92; 87,46</t>
+          <t>80,66; 87,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,08; 93,44</t>
+          <t>87,79; 93,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,05; 60,99</t>
+          <t>51,94; 61,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,75; 42,0</t>
+          <t>32,28; 42,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,5; 41,38</t>
+          <t>32,86; 41,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,88; 43,99</t>
+          <t>34,91; 44,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,13; 28,65</t>
+          <t>22,25; 28,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62,4; 68,5</t>
+          <t>62,52; 68,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57,87; 64,03</t>
+          <t>57,88; 63,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62,17; 68,93</t>
+          <t>62,32; 69,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,07; 41,99</t>
+          <t>36,02; 41,78</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>77,92; 88,88</t>
+          <t>77,81; 89,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,94; 66,44</t>
+          <t>53,78; 66,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,86; 78,83</t>
+          <t>69,26; 78,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,87; 49,99</t>
+          <t>41,47; 50,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,14; 42,64</t>
+          <t>22,53; 43,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,95; 33,15</t>
+          <t>18,65; 33,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,48; 51,22</t>
+          <t>39,05; 51,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,21; 87,36</t>
+          <t>31,31; 86,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60,17; 72,38</t>
+          <t>60,47; 72,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42,08; 52,38</t>
+          <t>42,56; 52,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58,94; 66,62</t>
+          <t>58,95; 66,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,33; 76,9</t>
+          <t>39,4; 76,43</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,17; 97,08</t>
+          <t>80,88; 96,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63,31; 90,88</t>
+          <t>64,54; 90,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,19; 93,55</t>
+          <t>75,58; 92,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54,89; 71,32</t>
+          <t>55,17; 71,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,39; 85,42</t>
+          <t>58,59; 86,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,13; 76,72</t>
+          <t>43,67; 77,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,79; 78,84</t>
+          <t>55,44; 80,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,07; 69,32</t>
+          <t>51,94; 69,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>74,74; 90,77</t>
+          <t>75,93; 91,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59,82; 81,22</t>
+          <t>59,54; 80,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,2; 84,58</t>
+          <t>69,85; 84,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56,64; 68,41</t>
+          <t>56,14; 67,85</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,54; 91,23</t>
+          <t>86,53; 91,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,2; 79,28</t>
+          <t>73,24; 79,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,86; 86,22</t>
+          <t>80,98; 86,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,76; 55,08</t>
+          <t>48,71; 55,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,09; 43,06</t>
+          <t>34,92; 42,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,27; 39,35</t>
+          <t>31,73; 39,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,0; 47,02</t>
+          <t>39,34; 47,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,77; 70,43</t>
+          <t>30,79; 74,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,44; 69,68</t>
+          <t>64,47; 69,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54,72; 60,06</t>
+          <t>55,02; 60,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62,96; 67,97</t>
+          <t>62,68; 67,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,65; 65,1</t>
+          <t>41,64; 65,66</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de jubilación</t>
+          <t>Población que, al menos, percibe una pensión de jubilación (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>447440; 473854</t>
+          <t>446945; 473421</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>444259; 480157</t>
+          <t>442849; 479628</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>387959; 411569</t>
+          <t>386680; 412218</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152573; 182294</t>
+          <t>155244; 183172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>147348; 188935</t>
+          <t>145204; 189351</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>174445; 222086</t>
+          <t>176354; 223044</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>144163; 187190</t>
+          <t>148535; 187981</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>83544; 108190</t>
+          <t>83995; 109132</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>599322; 657886</t>
+          <t>600413; 659506</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>628346; 695248</t>
+          <t>628440; 693458</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>538372; 596950</t>
+          <t>539660; 599077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>243964; 284017</t>
+          <t>243630; 282633</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>129840; 148119</t>
+          <t>129658; 148363</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>148580; 182998</t>
+          <t>148126; 183262</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>270738; 305492</t>
+          <t>268391; 305166</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>160271; 196054</t>
+          <t>162656; 197109</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19672; 36246</t>
+          <t>19153; 36950</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32346; 56576</t>
+          <t>31824; 56430</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>99022; 131816</t>
+          <t>100493; 132463</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>150972; 422540</t>
+          <t>151448; 416057</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>151416; 182131</t>
+          <t>152161; 182188</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>187733; 233687</t>
+          <t>189851; 233500</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380116; 429640</t>
+          <t>380194; 431348</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>344446; 673574</t>
+          <t>345128; 669399</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>49849; 58894</t>
+          <t>49064; 58755</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28886; 41463</t>
+          <t>29447; 41407</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51418; 64832</t>
+          <t>52375; 64433</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59467; 77268</t>
+          <t>59772; 77028</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24078; 35222</t>
+          <t>24158; 35709</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15343; 27294</t>
+          <t>15535; 27485</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28388; 41606</t>
+          <t>29258; 42580</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38517; 51281</t>
+          <t>38419; 51046</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76159; 92489</t>
+          <t>77372; 92895</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48577; 65955</t>
+          <t>48350; 65405</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84478; 103253</t>
+          <t>85276; 103451</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>103265; 124726</t>
+          <t>102352; 123710</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>638560; 673151</t>
+          <t>638499; 672924</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>636929; 689792</t>
+          <t>637236; 690164</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>725584; 773690</t>
+          <t>726670; 771837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>389792; 440321</t>
+          <t>389427; 439651</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>202158; 248046</t>
+          <t>201156; 247086</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>239760; 292369</t>
+          <t>235753; 291374</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>286860; 345881</t>
+          <t>289356; 348000</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>287804; 658728</t>
+          <t>287980; 694010</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>846704; 915506</t>
+          <t>847160; 914828</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>882591; 968882</t>
+          <t>887518; 968409</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1028163; 1109884</t>
+          <t>1023484; 1102623</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>722469; 1129292</t>
+          <t>722321; 1138947</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$jubilacion-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P62A$jubilacion-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,54; 92,72</t>
+          <t>87,4; 92,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,66; 87,36</t>
+          <t>80,83; 87,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,79; 93,58</t>
+          <t>88,09; 93,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,94; 61,29</t>
+          <t>51,74; 61,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,28; 42,09</t>
+          <t>32,61; 41,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,86; 41,55</t>
+          <t>32,97; 41,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,91; 44,18</t>
+          <t>34,26; 44,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,25; 28,9</t>
+          <t>22,29; 28,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62,52; 68,67</t>
+          <t>62,57; 68,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57,88; 63,87</t>
+          <t>58,14; 64,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62,32; 69,18</t>
+          <t>61,92; 68,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,02; 41,78</t>
+          <t>36,34; 42,05</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>77,81; 89,03</t>
+          <t>77,04; 88,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,78; 66,53</t>
+          <t>54,22; 66,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,26; 78,74</t>
+          <t>70,32; 79,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,47; 50,26</t>
+          <t>41,26; 50,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,53; 43,47</t>
+          <t>22,71; 43,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,65; 33,07</t>
+          <t>18,96; 33,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,05; 51,47</t>
+          <t>38,85; 51,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,31; 86,01</t>
+          <t>28,82; 37,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60,47; 72,4</t>
+          <t>59,89; 71,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42,56; 52,34</t>
+          <t>42,41; 52,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58,95; 66,89</t>
+          <t>58,9; 66,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,4; 76,43</t>
+          <t>37,46; 43,59</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,88; 96,86</t>
+          <t>80,98; 96,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,54; 90,75</t>
+          <t>62,54; 90,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75,58; 92,97</t>
+          <t>75,39; 92,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55,17; 71,1</t>
+          <t>55,77; 71,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,59; 86,6</t>
+          <t>58,93; 86,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,67; 77,26</t>
+          <t>41,55; 76,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,44; 80,68</t>
+          <t>53,14; 80,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,94; 69,01</t>
+          <t>52,78; 68,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>75,93; 91,17</t>
+          <t>76,09; 90,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59,54; 80,55</t>
+          <t>58,13; 80,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,85; 84,74</t>
+          <t>69,96; 85,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56,14; 67,85</t>
+          <t>57,3; 68,35</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>42,58%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,53; 91,2</t>
+          <t>86,66; 91,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,24; 79,32</t>
+          <t>73,27; 79,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,98; 86,02</t>
+          <t>80,65; 85,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,71; 55,0</t>
+          <t>49,25; 55,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,92; 42,89</t>
+          <t>35,11; 43,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,73; 39,22</t>
+          <t>32,28; 39,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,34; 47,31</t>
+          <t>39,85; 47,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,79; 74,21</t>
+          <t>29,53; 34,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,47; 69,62</t>
+          <t>64,7; 69,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55,02; 60,04</t>
+          <t>54,74; 60,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62,68; 67,52</t>
+          <t>62,9; 67,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,64; 65,66</t>
+          <t>40,6; 44,67</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168200</t>
+          <t>180635</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>96161</t>
+          <t>104957</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>264361</t>
+          <t>285591</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>446945; 473421</t>
+          <t>446248; 474445</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>442849; 479628</t>
+          <t>443750; 480217</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>386680; 412218</t>
+          <t>388002; 411584</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>155244; 183172</t>
+          <t>165961; 196472</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>145204; 189351</t>
+          <t>146685; 187931</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>176354; 223044</t>
+          <t>176945; 220669</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>148535; 187981</t>
+          <t>145784; 190482</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>83995; 109132</t>
+          <t>91614; 118436</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>600413; 659506</t>
+          <t>600923; 660951</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>628440; 693458</t>
+          <t>631298; 695513</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>539660; 599077</t>
+          <t>536221; 594823</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>243630; 282633</t>
+          <t>265987; 307749</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179423</t>
+          <t>195681</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>295183</t>
+          <t>100479</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>474606</t>
+          <t>296160</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>129658; 148363</t>
+          <t>128379; 147518</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>148126; 183262</t>
+          <t>149343; 183271</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>268391; 305166</t>
+          <t>272512; 306945</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>162656; 197109</t>
+          <t>176480; 214027</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19153; 36950</t>
+          <t>19304; 36692</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31824; 56430</t>
+          <t>32363; 56525</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>100493; 132463</t>
+          <t>99981; 132223</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>151448; 416057</t>
+          <t>87787; 113549</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>152161; 182188</t>
+          <t>150699; 180700</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>189851; 233500</t>
+          <t>189214; 234802</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380194; 431348</t>
+          <t>379866; 428240</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>345128; 669399</t>
+          <t>274325; 319226</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68683</t>
+          <t>78461</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44740</t>
+          <t>52183</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>113424</t>
+          <t>130644</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>49064; 58755</t>
+          <t>49127; 58822</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29447; 41407</t>
+          <t>28535; 41321</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52375; 64433</t>
+          <t>52249; 64419</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59772; 77028</t>
+          <t>68582; 88260</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24158; 35709</t>
+          <t>24299; 35653</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15535; 27485</t>
+          <t>14782; 27128</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29258; 42580</t>
+          <t>28047; 42331</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38419; 51046</t>
+          <t>45222; 58617</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>77372; 92895</t>
+          <t>77533; 92517</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48350; 65405</t>
+          <t>47202; 65664</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85276; 103451</t>
+          <t>85403; 104344</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>102352; 123710</t>
+          <t>119545; 142604</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>416308</t>
+          <t>454776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>436084</t>
+          <t>257619</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>852391</t>
+          <t>712395</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>638499; 672924</t>
+          <t>639437; 672786</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>637236; 690164</t>
+          <t>637542; 690588</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>726670; 771837</t>
+          <t>723647; 770361</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>389427; 439651</t>
+          <t>429254; 484663</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>201156; 247086</t>
+          <t>202254; 249874</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>235753; 291374</t>
+          <t>239858; 293169</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>289356; 348000</t>
+          <t>293164; 348988</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>287980; 694010</t>
+          <t>236605; 276298</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>847160; 914828</t>
+          <t>850179; 919693</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>887518; 968409</t>
+          <t>882982; 968649</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1023484; 1102623</t>
+          <t>1027050; 1104839</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>722321; 1138947</t>
+          <t>679146; 747210</t>
         </is>
       </c>
     </row>
